--- a/food_beverage_order_forms/019_steak_order_form--food_beverage_order_forms.xlsx
+++ b/food_beverage_order_forms/019_steak_order_form--food_beverage_order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -688,8 +688,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="29" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -717,12 +717,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'customer_name'}</t>
+          <t>customer_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'customer_name'}</t>
+          <t>customer name</t>
         </is>
       </c>
     </row>
@@ -734,12 +734,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'email'}</t>
+          <t>email</t>
         </is>
       </c>
     </row>
@@ -751,12 +751,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'rare'}</t>
+          <t>rare</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'rare'}</t>
+          <t>rare</t>
         </is>
       </c>
     </row>
@@ -768,12 +768,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'medium_rare'}</t>
+          <t>medium_rare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'medium_rare'}</t>
+          <t>medium rare</t>
         </is>
       </c>
     </row>
@@ -785,12 +785,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'well_done'}</t>
+          <t>well_done</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'well_done'}</t>
+          <t>well done</t>
         </is>
       </c>
     </row>
@@ -802,12 +802,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'card_number'}</t>
+          <t>card_number</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'card_number'}</t>
+          <t>card number</t>
         </is>
       </c>
     </row>
@@ -819,12 +819,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'expiration_date'}</t>
+          <t>expiration_date</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'expiration_date'}</t>
+          <t>expiration date</t>
         </is>
       </c>
     </row>
@@ -836,12 +836,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'cvv'}</t>
+          <t>cvv</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'cvv'}</t>
+          <t>cvv</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'quantity'}</t>
+          <t>quantity</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'quantity'}</t>
+          <t>quantity</t>
         </is>
       </c>
     </row>
@@ -870,12 +870,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'order_date'}</t>
+          <t>order_date</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'order_date'}</t>
+          <t>order date</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'delivery_time'}</t>
+          <t>delivery_time</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'delivery_time'}</t>
+          <t>delivery time</t>
         </is>
       </c>
     </row>
@@ -904,12 +904,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'address'}</t>
+          <t>address</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'address'}</t>
+          <t>address</t>
         </is>
       </c>
     </row>
